--- a/templates/企業健診プラン.xlsx
+++ b/templates/企業健診プラン.xlsx
@@ -74,7 +74,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -96,11 +96,128 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,6 +253,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,24 +660,24 @@
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="14" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="4" t="n"/>
+      <c r="I2" s="14" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>受診日</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="4" t="n"/>
+      <c r="L2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -558,24 +686,24 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="14" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>既往歴</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="14" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>自覚症状</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13" t="n"/>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -593,7 +721,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
+      <c r="D4" s="14" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -619,7 +747,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n"/>
+      <c r="J4" s="14" t="n"/>
       <c r="K4" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -675,7 +803,7 @@
           <t>18.5-24.9 / 89.9以下</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="15" t="n"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>GPT(ALT)(U/L)</t>
@@ -689,7 +817,7 @@
           <t>30以下</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n"/>
+      <c r="L6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -705,7 +833,7 @@
           <t>129以下</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="15" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>γ-GTP(U/L)</t>
@@ -719,7 +847,7 @@
           <t>50以下</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n"/>
+      <c r="L7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -735,13 +863,13 @@
           <t>84以下</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="16" t="n"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="4" t="n"/>
+      <c r="L8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -759,7 +887,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="14" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -785,7 +913,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n"/>
+      <c r="J9" s="14" t="n"/>
       <c r="K9" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -841,7 +969,7 @@
           <t>30以下</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="15" t="n"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>HDLコレステロール(mg/dL)</t>
@@ -855,7 +983,7 @@
           <t>40以上</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n"/>
+      <c r="L11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -871,7 +999,7 @@
           <t>30以下</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>中性脂肪(mg/dL)</t>
@@ -885,7 +1013,7 @@
           <t>30-149</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n"/>
+      <c r="L12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -903,7 +1031,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
+      <c r="D13" s="14" t="n"/>
       <c r="E13" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -929,7 +1057,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="14" t="n"/>
       <c r="K13" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -981,7 +1109,7 @@
           <t>376-500</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="15" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
           <t>尿素窒素(BUN)(mg/dL)</t>
@@ -991,7 +1119,7 @@
       <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr"/>
       <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="4" t="n"/>
+      <c r="L15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1007,7 +1135,7 @@
           <t>12.1-14.5</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="15" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>クレアチニン(mg/dL)</t>
@@ -1017,7 +1145,7 @@
       <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="4" t="n"/>
+      <c r="L16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1033,7 +1161,7 @@
           <t>基準内</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
+      <c r="F17" s="16" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>eGFR(mL/min/1.73m2)</t>
@@ -1043,7 +1171,7 @@
       <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr"/>
       <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="4" t="n"/>
+      <c r="L17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1061,7 +1189,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n"/>
+      <c r="D18" s="14" t="n"/>
       <c r="E18" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1087,7 +1215,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="14" t="n"/>
       <c r="K18" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1131,7 +1259,7 @@
       <c r="C20" s="8" t="inlineStr"/>
       <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="15" t="n"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>便潜血(1日法)</t>
@@ -1141,7 +1269,7 @@
       <c r="I20" s="8" t="inlineStr"/>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="4" t="n"/>
+      <c r="L20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1153,7 +1281,7 @@
       <c r="C21" s="8" t="inlineStr"/>
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="F21" s="16" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>総蛋白(g/dL) / アルブミン(g/dL)</t>
@@ -1163,7 +1291,7 @@
       <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="inlineStr"/>
       <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="4" t="n"/>
+      <c r="L21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1181,7 +1309,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n"/>
+      <c r="D22" s="14" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1223,7 +1351,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n"/>
+      <c r="F24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1231,48 +1359,49 @@
           <t>【医師の総合所見】</t>
         </is>
       </c>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="9" t="inlineStr"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+      <c r="L26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
+      <c r="A27" s="19" t="n"/>
+      <c r="L27" s="20" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
+      <c r="A28" s="21" t="n"/>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -1284,14 +1413,14 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>医療法人あんず会 杏クリニック　〒350-1307 埼玉県狭山市祇園25-1 第一はまビル3階</t>
+          <t>医療法人○○会 ○○クリニック　〒000-0000 ○○県○○市○○町0-0-0 ○○ビル0階</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>院長 鬼澤 信之　印</t>
+          <t>院長 ○○ ○○　印</t>
         </is>
       </c>
     </row>
@@ -1306,10 +1435,10 @@
     <mergeCell ref="F10:F12"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="F23:F24"/>
+    <mergeCell ref="A26:L28"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F19:F21"/>
     <mergeCell ref="L14:L17"/>
-    <mergeCell ref="A26:L28"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="L5:L8"/>
     <mergeCell ref="A29:L29"/>
@@ -1375,10 +1504,10 @@
           <t>サンプル 太郎 (ID: 000000000)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="14" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>生年月日</t>
@@ -1389,7 +1518,7 @@
           <t>S50.01.01 (51歳)</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n"/>
+      <c r="I2" s="14" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>受診日</t>
@@ -1400,7 +1529,7 @@
           <t>2026年6月25日</t>
         </is>
       </c>
-      <c r="L2" s="4" t="n"/>
+      <c r="L2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1413,7 +1542,7 @@
           <t>男性</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="14" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>既往歴</t>
@@ -1424,7 +1553,7 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="14" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>自覚症状</t>
@@ -1435,10 +1564,10 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13" t="n"/>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1456,7 +1585,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
+      <c r="D4" s="14" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1482,7 +1611,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n"/>
+      <c r="J4" s="14" t="n"/>
       <c r="K4" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1574,7 +1703,7 @@
           <t>18.5-24.9 / 89.9以下</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="15" t="n"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>GPT(ALT)(U/L)</t>
@@ -1596,7 +1725,7 @@
           <t>30以下</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n"/>
+      <c r="L6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1620,7 +1749,7 @@
           <t>129以下</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="15" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>γ-GTP(U/L)</t>
@@ -1642,7 +1771,7 @@
           <t>50以下</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n"/>
+      <c r="L7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1666,13 +1795,13 @@
           <t>84以下</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="16" t="n"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="4" t="n"/>
+      <c r="L8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1690,7 +1819,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="14" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1716,7 +1845,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n"/>
+      <c r="J9" s="14" t="n"/>
       <c r="K9" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1812,7 +1941,7 @@
           <t>30以下</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="15" t="n"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>HDLコレステロール(mg/dL)</t>
@@ -1834,7 +1963,7 @@
           <t>40以上</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n"/>
+      <c r="L11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1862,7 +1991,7 @@
           <t>30以下</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>中性脂肪(mg/dL)</t>
@@ -1884,7 +2013,7 @@
           <t>30-149</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n"/>
+      <c r="L12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1902,7 +2031,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
+      <c r="D13" s="14" t="n"/>
       <c r="E13" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -1928,7 +2057,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="14" t="n"/>
       <c r="K13" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -2016,7 +2145,7 @@
           <t>376-500</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="15" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
           <t>尿素窒素(BUN)(mg/dL)</t>
@@ -2030,7 +2159,7 @@
       <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr"/>
       <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="4" t="n"/>
+      <c r="L15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -2054,7 +2183,7 @@
           <t>12.1-14.5</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="15" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>クレアチニン(mg/dL)</t>
@@ -2068,7 +2197,7 @@
       <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="4" t="n"/>
+      <c r="L16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2092,7 +2221,7 @@
           <t>基準内</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
+      <c r="F17" s="16" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>eGFR(mL/min/1.73m2)</t>
@@ -2106,7 +2235,7 @@
       <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr"/>
       <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="4" t="n"/>
+      <c r="L17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2124,7 +2253,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n"/>
+      <c r="D18" s="14" t="n"/>
       <c r="E18" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -2150,7 +2279,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="14" t="n"/>
       <c r="K18" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -2214,7 +2343,7 @@
       <c r="C20" s="8" t="inlineStr"/>
       <c r="D20" s="8" t="inlineStr"/>
       <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="15" t="n"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>便潜血(1日法)</t>
@@ -2228,7 +2357,7 @@
       <c r="I20" s="8" t="inlineStr"/>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="4" t="n"/>
+      <c r="L20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2244,7 +2373,7 @@
       <c r="C21" s="8" t="inlineStr"/>
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="F21" s="16" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>総蛋白(g/dL) / アルブミン(g/dL)</t>
@@ -2258,7 +2387,7 @@
       <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="inlineStr"/>
       <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="4" t="n"/>
+      <c r="L21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2276,7 +2405,7 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n"/>
+      <c r="D22" s="14" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
           <t>基準範囲</t>
@@ -2330,7 +2459,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n"/>
+      <c r="F24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2338,6 +2467,17 @@
           <t>【医師の総合所見】</t>
         </is>
       </c>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="14" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -2345,45 +2485,35 @@
           <t>特記すべき異常を認めません。現在の生活習慣を維持してください。</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+      <c r="L26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
+      <c r="A27" s="19" t="n"/>
+      <c r="L27" s="20" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
+      <c r="A28" s="21" t="n"/>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -2395,14 +2525,14 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>医療法人あんず会 杏クリニック　〒350-1307 埼玉県狭山市祇園25-1 第一はまビル3階</t>
+          <t>医療法人○○会 ○○クリニック　〒000-0000 ○○県○○市○○町0-0-0 ○○ビル0階</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>院長 鬼澤 信之　印</t>
+          <t>院長 ○○ ○○　印</t>
         </is>
       </c>
     </row>
@@ -2417,10 +2547,10 @@
     <mergeCell ref="F10:F12"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="F23:F24"/>
+    <mergeCell ref="A26:L28"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F19:F21"/>
     <mergeCell ref="L14:L17"/>
-    <mergeCell ref="A26:L28"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="L5:L8"/>
     <mergeCell ref="A29:L29"/>
